--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19050" windowHeight="8085" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t>CA not done</t>
+  </si>
+  <si>
+    <t>Feeling a little tired.</t>
   </si>
 </sst>
 </file>
@@ -3664,26 +3667,50 @@
       </c>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" s="11"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="13" t="str">
+      <c r="A49" s="11">
+        <v>46286</v>
+      </c>
+      <c r="B49" s="12">
+        <v>390</v>
+      </c>
+      <c r="C49" s="12">
+        <v>20</v>
+      </c>
+      <c r="D49" s="12">
+        <v>120</v>
+      </c>
+      <c r="E49" s="12">
+        <v>30</v>
+      </c>
+      <c r="F49" s="12">
+        <v>250</v>
+      </c>
+      <c r="G49" s="12">
+        <v>5</v>
+      </c>
+      <c r="H49" s="12">
+        <v>30</v>
+      </c>
+      <c r="I49" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="13" t="str">
+        <v>840</v>
+      </c>
+      <c r="J49" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
-      <c r="N49" s="15"/>
+        <v>600</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L49" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="N49" s="15" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19050" windowHeight="8085" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>Feeling a little tired.</t>
+  </si>
+  <si>
+    <t>Preparing for CA.</t>
   </si>
 </sst>
 </file>
@@ -3713,26 +3716,50 @@
       </c>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="11"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-      <c r="I50" s="13" t="str">
+      <c r="A50" s="11">
+        <v>46287</v>
+      </c>
+      <c r="B50" s="12">
+        <v>300</v>
+      </c>
+      <c r="C50" s="12">
+        <v>20</v>
+      </c>
+      <c r="D50" s="12">
+        <v>90</v>
+      </c>
+      <c r="E50" s="12">
+        <v>40</v>
+      </c>
+      <c r="F50" s="12">
+        <v>350</v>
+      </c>
+      <c r="G50" s="12">
+        <v>7</v>
+      </c>
+      <c r="H50" s="12">
+        <v>30</v>
+      </c>
+      <c r="I50" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="13" t="str">
+        <v>830</v>
+      </c>
+      <c r="J50" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
-      <c r="N50" s="15"/>
+        <v>610</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L50" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M50" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N50" s="15" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>Preparing for CA.</t>
+  </si>
+  <si>
+    <t>Feeling good.</t>
   </si>
 </sst>
 </file>
@@ -3762,26 +3765,50 @@
       </c>
     </row>
     <row r="51" spans="1:14">
-      <c r="A51" s="11"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-      <c r="I51" s="13" t="str">
+      <c r="A51" s="11">
+        <v>46288</v>
+      </c>
+      <c r="B51" s="12">
+        <v>420</v>
+      </c>
+      <c r="C51" s="12">
+        <v>30</v>
+      </c>
+      <c r="D51" s="12">
+        <v>110</v>
+      </c>
+      <c r="E51" s="12">
+        <v>40</v>
+      </c>
+      <c r="F51" s="12">
+        <v>300</v>
+      </c>
+      <c r="G51" s="12">
+        <v>6</v>
+      </c>
+      <c r="H51" s="12">
+        <v>40</v>
+      </c>
+      <c r="I51" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="13" t="str">
+        <v>940</v>
+      </c>
+      <c r="J51" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
-      <c r="M51" s="14"/>
-      <c r="N51" s="15"/>
+        <v>500</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L51" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M51" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N51" s="15" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>Feeling good.</t>
+  </si>
+  <si>
+    <t>Preparing for CA and viva.</t>
   </si>
 </sst>
 </file>
@@ -3811,26 +3814,50 @@
       </c>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="11"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="13" t="str">
+      <c r="A52" s="11">
+        <v>46289</v>
+      </c>
+      <c r="B52" s="12">
+        <v>390</v>
+      </c>
+      <c r="C52" s="12">
+        <v>20</v>
+      </c>
+      <c r="D52" s="12">
+        <v>120</v>
+      </c>
+      <c r="E52" s="12">
+        <v>40</v>
+      </c>
+      <c r="F52" s="12">
+        <v>100</v>
+      </c>
+      <c r="G52" s="12">
+        <v>2</v>
+      </c>
+      <c r="H52" s="12">
+        <v>25</v>
+      </c>
+      <c r="I52" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="13" t="str">
+        <v>695</v>
+      </c>
+      <c r="J52" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-      <c r="M52" s="14"/>
-      <c r="N52" s="15"/>
+        <v>745</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L52" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M52" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N52" s="15" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>Preparing for CA and viva.</t>
+  </si>
+  <si>
+    <t>Little bit tired.</t>
   </si>
 </sst>
 </file>
@@ -3860,26 +3863,50 @@
       </c>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" s="11"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="13" t="str">
+      <c r="A53" s="11">
+        <v>46290</v>
+      </c>
+      <c r="B53" s="12">
+        <v>380</v>
+      </c>
+      <c r="C53" s="12">
+        <v>20</v>
+      </c>
+      <c r="D53" s="12">
+        <v>90</v>
+      </c>
+      <c r="E53" s="12">
+        <v>120</v>
+      </c>
+      <c r="F53" s="12">
+        <v>250</v>
+      </c>
+      <c r="G53" s="12">
+        <v>5</v>
+      </c>
+      <c r="H53" s="12">
+        <v>30</v>
+      </c>
+      <c r="I53" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="13" t="str">
+        <v>890</v>
+      </c>
+      <c r="J53" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-      <c r="N53" s="15"/>
+        <v>550</v>
+      </c>
+      <c r="K53" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L53" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M53" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N53" s="15" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20370" windowHeight="8520" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -3909,21 +3909,37 @@
       </c>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" s="11"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="13" t="str">
+      <c r="A54" s="11">
+        <v>46290</v>
+      </c>
+      <c r="B54" s="12">
+        <v>360</v>
+      </c>
+      <c r="C54" s="12">
+        <v>30</v>
+      </c>
+      <c r="D54" s="12">
+        <v>50</v>
+      </c>
+      <c r="E54" s="12">
+        <v>30</v>
+      </c>
+      <c r="F54" s="12">
+        <v>150</v>
+      </c>
+      <c r="G54" s="12">
+        <v>3</v>
+      </c>
+      <c r="H54" s="12">
+        <v>30</v>
+      </c>
+      <c r="I54" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="13" t="str">
+        <v>650</v>
+      </c>
+      <c r="J54" s="13">
         <f t="shared" si="1"/>
-        <v/>
+        <v>790</v>
       </c>
       <c r="K54" s="14"/>
       <c r="L54" s="14"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20370" windowHeight="8520" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20370" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>Little bit tired.</t>
+  </si>
+  <si>
+    <t>Scared because something happened suddenly in university.</t>
   </si>
 </sst>
 </file>
@@ -3910,7 +3913,7 @@
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="11">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B54" s="12">
         <v>360</v>
@@ -3941,32 +3944,64 @@
         <f t="shared" si="1"/>
         <v>790</v>
       </c>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
-      <c r="N54" s="15"/>
-    </row>
-    <row r="55" spans="1:14">
-      <c r="A55" s="11"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="13" t="str">
+      <c r="K54" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L54" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M54" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N54" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" ht="45" spans="1:14">
+      <c r="A55" s="11">
+        <v>46292</v>
+      </c>
+      <c r="B55" s="12">
+        <v>280</v>
+      </c>
+      <c r="C55" s="12">
+        <v>30</v>
+      </c>
+      <c r="D55" s="12">
+        <v>120</v>
+      </c>
+      <c r="E55" s="12">
+        <v>30</v>
+      </c>
+      <c r="F55" s="12">
+        <v>0</v>
+      </c>
+      <c r="G55" s="12">
+        <v>0</v>
+      </c>
+      <c r="H55" s="12">
+        <v>30</v>
+      </c>
+      <c r="I55" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="13" t="str">
+        <v>490</v>
+      </c>
+      <c r="J55" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
-      <c r="M55" s="14"/>
-      <c r="N55" s="15"/>
+        <v>950</v>
+      </c>
+      <c r="K55" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L55" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M55" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="N55" s="15" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20370" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20370" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>Scared because something happened suddenly in university.</t>
+  </si>
+  <si>
+    <t>Feeling good because going home.</t>
   </si>
 </sst>
 </file>
@@ -4003,27 +4006,51 @@
         <v>88</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
-      <c r="A56" s="11"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-      <c r="I56" s="13" t="str">
+    <row r="56" ht="30" spans="1:14">
+      <c r="A56" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B56" s="12">
+        <v>360</v>
+      </c>
+      <c r="C56" s="12">
+        <v>30</v>
+      </c>
+      <c r="D56" s="12">
+        <v>60</v>
+      </c>
+      <c r="E56" s="12">
+        <v>10</v>
+      </c>
+      <c r="F56" s="12">
+        <v>0</v>
+      </c>
+      <c r="G56" s="12">
+        <v>0</v>
+      </c>
+      <c r="H56" s="12">
+        <v>20</v>
+      </c>
+      <c r="I56" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="13" t="str">
+        <v>480</v>
+      </c>
+      <c r="J56" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="14"/>
-      <c r="N56" s="15"/>
+        <v>960</v>
+      </c>
+      <c r="K56" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L56" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M56" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N56" s="15" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20370" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20370" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>Feeling good because going home.</t>
+  </si>
+  <si>
+    <t>Had a normal day.</t>
   </si>
 </sst>
 </file>
@@ -4053,26 +4056,50 @@
       </c>
     </row>
     <row r="57" spans="1:14">
-      <c r="A57" s="11"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="13" t="str">
+      <c r="A57" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B57" s="12">
+        <v>480</v>
+      </c>
+      <c r="C57" s="12">
+        <v>20</v>
+      </c>
+      <c r="D57" s="12">
+        <v>60</v>
+      </c>
+      <c r="E57" s="12">
+        <v>20</v>
+      </c>
+      <c r="F57" s="12">
+        <v>0</v>
+      </c>
+      <c r="G57" s="12">
+        <v>0</v>
+      </c>
+      <c r="H57" s="12">
+        <v>20</v>
+      </c>
+      <c r="I57" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="13" t="str">
+        <v>600</v>
+      </c>
+      <c r="J57" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-      <c r="M57" s="14"/>
-      <c r="N57" s="15"/>
+        <v>840</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L57" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M57" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N57" s="15" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20370" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20370" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4102,26 +4102,50 @@
       </c>
     </row>
     <row r="58" spans="1:14">
-      <c r="A58" s="11"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-      <c r="I58" s="13" t="str">
+      <c r="A58" s="11">
+        <v>46295</v>
+      </c>
+      <c r="B58" s="12">
+        <v>390</v>
+      </c>
+      <c r="C58" s="12">
+        <v>20</v>
+      </c>
+      <c r="D58" s="12">
+        <v>100</v>
+      </c>
+      <c r="E58" s="12">
+        <v>20</v>
+      </c>
+      <c r="F58" s="12">
+        <v>0</v>
+      </c>
+      <c r="G58" s="12">
+        <v>0</v>
+      </c>
+      <c r="H58" s="12">
+        <v>20</v>
+      </c>
+      <c r="I58" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="13" t="str">
+        <v>550</v>
+      </c>
+      <c r="J58" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="14"/>
-      <c r="N58" s="15"/>
+        <v>890</v>
+      </c>
+      <c r="K58" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L58" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M58" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N58" s="15" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20370" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20370" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>Had a normal day.</t>
+  </si>
+  <si>
+    <t>Completed my routine.</t>
   </si>
 </sst>
 </file>
@@ -4148,26 +4151,50 @@
       </c>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" s="11"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="13" t="str">
+      <c r="A59" s="11">
+        <v>46296</v>
+      </c>
+      <c r="B59" s="12">
+        <v>330</v>
+      </c>
+      <c r="C59" s="12">
+        <v>20</v>
+      </c>
+      <c r="D59" s="12">
+        <v>120</v>
+      </c>
+      <c r="E59" s="12">
+        <v>20</v>
+      </c>
+      <c r="F59" s="12">
+        <v>0</v>
+      </c>
+      <c r="G59" s="12">
+        <v>0</v>
+      </c>
+      <c r="H59" s="12">
+        <v>20</v>
+      </c>
+      <c r="I59" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="13" t="str">
+        <v>510</v>
+      </c>
+      <c r="J59" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="14"/>
-      <c r="L59" s="14"/>
-      <c r="M59" s="14"/>
-      <c r="N59" s="15"/>
+        <v>930</v>
+      </c>
+      <c r="K59" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L59" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M59" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N59" s="15" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20370" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t>Completed my routine.</t>
+  </si>
+  <si>
+    <t>Had a peacefull day.</t>
   </si>
 </sst>
 </file>
@@ -4197,26 +4200,50 @@
       </c>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
-      <c r="I60" s="13" t="str">
+      <c r="A60" s="11">
+        <v>46297</v>
+      </c>
+      <c r="B60" s="12">
+        <v>300</v>
+      </c>
+      <c r="C60" s="12">
+        <v>20</v>
+      </c>
+      <c r="D60" s="12">
+        <v>100</v>
+      </c>
+      <c r="E60" s="12">
+        <v>20</v>
+      </c>
+      <c r="F60" s="12">
+        <v>0</v>
+      </c>
+      <c r="G60" s="12">
+        <v>0</v>
+      </c>
+      <c r="H60" s="12">
+        <v>20</v>
+      </c>
+      <c r="I60" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="13" t="str">
+        <v>460</v>
+      </c>
+      <c r="J60" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
-      <c r="N60" s="15"/>
+        <v>980</v>
+      </c>
+      <c r="K60" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L60" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M60" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N60" s="15" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>Had a peacefull day.</t>
+  </si>
+  <si>
+    <t>Good use of time.</t>
   </si>
 </sst>
 </file>
@@ -4246,26 +4249,50 @@
       </c>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="11"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-      <c r="I61" s="13" t="str">
+      <c r="A61" s="11">
+        <v>46298</v>
+      </c>
+      <c r="B61" s="12">
+        <v>310</v>
+      </c>
+      <c r="C61" s="12">
+        <v>20</v>
+      </c>
+      <c r="D61" s="12">
+        <v>60</v>
+      </c>
+      <c r="E61" s="12">
+        <v>20</v>
+      </c>
+      <c r="F61" s="12">
+        <v>0</v>
+      </c>
+      <c r="G61" s="12">
+        <v>0</v>
+      </c>
+      <c r="H61" s="12">
+        <v>30</v>
+      </c>
+      <c r="I61" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="13" t="str">
+        <v>440</v>
+      </c>
+      <c r="J61" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="14"/>
-      <c r="N61" s="15"/>
+        <v>1000</v>
+      </c>
+      <c r="K61" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L61" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M61" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N61" s="15" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>Good use of time.</t>
+  </si>
+  <si>
+    <t>Need to focus more on study.</t>
   </si>
 </sst>
 </file>
@@ -4295,26 +4298,50 @@
       </c>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="11"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-      <c r="I62" s="13" t="str">
+      <c r="A62" s="11">
+        <v>46299</v>
+      </c>
+      <c r="B62" s="12">
+        <v>360</v>
+      </c>
+      <c r="C62" s="12">
+        <v>20</v>
+      </c>
+      <c r="D62" s="12">
+        <v>120</v>
+      </c>
+      <c r="E62" s="12">
+        <v>30</v>
+      </c>
+      <c r="F62" s="12">
+        <v>0</v>
+      </c>
+      <c r="G62" s="12">
+        <v>0</v>
+      </c>
+      <c r="H62" s="12">
+        <v>20</v>
+      </c>
+      <c r="I62" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="13" t="str">
+        <v>550</v>
+      </c>
+      <c r="J62" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-      <c r="N62" s="15"/>
+        <v>890</v>
+      </c>
+      <c r="K62" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="L62" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M62" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N62" s="15" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -313,6 +313,9 @@
   </si>
   <si>
     <t>Need to focus more on study.</t>
+  </si>
+  <si>
+    <t>I'm a little worried because of my Python project.</t>
   </si>
 </sst>
 </file>
@@ -4343,27 +4346,51 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
-      <c r="A63" s="11"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12"/>
-      <c r="I63" s="13" t="str">
+    <row r="63" ht="30" spans="1:14">
+      <c r="A63" s="11">
+        <v>46300</v>
+      </c>
+      <c r="B63" s="12">
+        <v>300</v>
+      </c>
+      <c r="C63" s="12">
+        <v>20</v>
+      </c>
+      <c r="D63" s="12">
+        <v>150</v>
+      </c>
+      <c r="E63" s="12">
+        <v>120</v>
+      </c>
+      <c r="F63" s="12">
+        <v>0</v>
+      </c>
+      <c r="G63" s="12">
+        <v>0</v>
+      </c>
+      <c r="H63" s="12">
+        <v>20</v>
+      </c>
+      <c r="I63" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="13" t="str">
+        <v>610</v>
+      </c>
+      <c r="J63" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="14"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="14"/>
-      <c r="N63" s="15"/>
+        <v>830</v>
+      </c>
+      <c r="K63" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L63" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M63" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N63" s="15" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4363,21 +4363,21 @@
         <v>120</v>
       </c>
       <c r="F63" s="12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G63" s="12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H63" s="12">
         <v>20</v>
       </c>
       <c r="I63" s="13">
         <f t="shared" si="0"/>
-        <v>610</v>
+        <v>860</v>
       </c>
       <c r="J63" s="13">
         <f t="shared" si="1"/>
-        <v>830</v>
+        <v>580</v>
       </c>
       <c r="K63" s="14" t="s">
         <v>79</v>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t>I'm a little worried because of my Python project.</t>
+  </si>
+  <si>
+    <t>Missed one class.</t>
   </si>
 </sst>
 </file>
@@ -4393,26 +4396,50 @@
       </c>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="11"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12"/>
-      <c r="I64" s="13" t="str">
+      <c r="A64" s="11">
+        <v>46301</v>
+      </c>
+      <c r="B64" s="12">
+        <v>300</v>
+      </c>
+      <c r="C64" s="12">
+        <v>20</v>
+      </c>
+      <c r="D64" s="12">
+        <v>80</v>
+      </c>
+      <c r="E64" s="12">
+        <v>60</v>
+      </c>
+      <c r="F64" s="12">
+        <v>300</v>
+      </c>
+      <c r="G64" s="12">
+        <v>6</v>
+      </c>
+      <c r="H64" s="12">
+        <v>30</v>
+      </c>
+      <c r="I64" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="13" t="str">
+        <v>790</v>
+      </c>
+      <c r="J64" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="14"/>
-      <c r="L64" s="14"/>
-      <c r="M64" s="14"/>
-      <c r="N64" s="15"/>
+        <v>650</v>
+      </c>
+      <c r="K64" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L64" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M64" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N64" s="15" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t>Missed one class.</t>
+  </si>
+  <si>
+    <t>Attend my all classes.</t>
   </si>
 </sst>
 </file>
@@ -4442,26 +4445,50 @@
       </c>
     </row>
     <row r="65" spans="1:14">
-      <c r="A65" s="11"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12"/>
-      <c r="I65" s="13" t="str">
+      <c r="A65" s="11">
+        <v>46302</v>
+      </c>
+      <c r="B65" s="12">
+        <v>420</v>
+      </c>
+      <c r="C65" s="12">
+        <v>20</v>
+      </c>
+      <c r="D65" s="12">
+        <v>60</v>
+      </c>
+      <c r="E65" s="12">
+        <v>20</v>
+      </c>
+      <c r="F65" s="12">
+        <v>350</v>
+      </c>
+      <c r="G65" s="12">
+        <v>7</v>
+      </c>
+      <c r="H65" s="12">
+        <v>20</v>
+      </c>
+      <c r="I65" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="13" t="str">
+        <v>890</v>
+      </c>
+      <c r="J65" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="14"/>
-      <c r="L65" s="14"/>
-      <c r="M65" s="14"/>
-      <c r="N65" s="15"/>
+        <v>550</v>
+      </c>
+      <c r="K65" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L65" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M65" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N65" s="15" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4491,26 +4491,50 @@
       </c>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="11"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
-      <c r="I66" s="13" t="str">
+      <c r="A66" s="11">
+        <v>46303</v>
+      </c>
+      <c r="B66" s="12">
+        <v>240</v>
+      </c>
+      <c r="C66" s="12">
+        <v>40</v>
+      </c>
+      <c r="D66" s="12">
+        <v>120</v>
+      </c>
+      <c r="E66" s="12">
+        <v>20</v>
+      </c>
+      <c r="F66" s="12">
+        <v>150</v>
+      </c>
+      <c r="G66" s="12">
+        <v>3</v>
+      </c>
+      <c r="H66" s="12">
+        <v>30</v>
+      </c>
+      <c r="I66" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="13" t="str">
+        <v>600</v>
+      </c>
+      <c r="J66" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="14"/>
-      <c r="L66" s="14"/>
-      <c r="M66" s="14"/>
-      <c r="N66" s="15"/>
+        <v>840</v>
+      </c>
+      <c r="K66" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L66" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M66" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N66" s="15" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>Attend my all classes.</t>
+  </si>
+  <si>
+    <t>Feeling great today.</t>
   </si>
 </sst>
 </file>
@@ -4537,26 +4540,50 @@
       </c>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" s="11"/>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12"/>
-      <c r="I67" s="13" t="str">
+      <c r="A67" s="11">
+        <v>46304</v>
+      </c>
+      <c r="B67" s="12">
+        <v>480</v>
+      </c>
+      <c r="C67" s="12">
+        <v>20</v>
+      </c>
+      <c r="D67" s="12">
+        <v>60</v>
+      </c>
+      <c r="E67" s="12">
+        <v>20</v>
+      </c>
+      <c r="F67" s="12">
+        <v>0</v>
+      </c>
+      <c r="G67" s="12">
+        <v>0</v>
+      </c>
+      <c r="H67" s="12">
+        <v>30</v>
+      </c>
+      <c r="I67" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="13" t="str">
+        <v>610</v>
+      </c>
+      <c r="J67" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="14"/>
-      <c r="L67" s="14"/>
-      <c r="M67" s="14"/>
-      <c r="N67" s="15"/>
+        <v>830</v>
+      </c>
+      <c r="K67" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L67" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M67" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N67" s="15" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4586,48 +4586,96 @@
       </c>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="11"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12"/>
-      <c r="I68" s="13" t="str">
+      <c r="A68" s="11">
+        <v>46305</v>
+      </c>
+      <c r="B68" s="12">
+        <v>360</v>
+      </c>
+      <c r="C68" s="12">
+        <v>30</v>
+      </c>
+      <c r="D68" s="12">
+        <v>120</v>
+      </c>
+      <c r="E68" s="12">
+        <v>20</v>
+      </c>
+      <c r="F68" s="12">
+        <v>0</v>
+      </c>
+      <c r="G68" s="12">
+        <v>0</v>
+      </c>
+      <c r="H68" s="12">
+        <v>30</v>
+      </c>
+      <c r="I68" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="13" t="str">
+        <v>560</v>
+      </c>
+      <c r="J68" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="14"/>
-      <c r="L68" s="14"/>
-      <c r="M68" s="14"/>
-      <c r="N68" s="15"/>
+        <v>880</v>
+      </c>
+      <c r="K68" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L68" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M68" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N68" s="15" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="69" spans="1:14">
-      <c r="A69" s="11"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12"/>
-      <c r="I69" s="13" t="str">
+      <c r="A69" s="11">
+        <v>46306</v>
+      </c>
+      <c r="B69" s="12">
+        <v>300</v>
+      </c>
+      <c r="C69" s="12">
+        <v>30</v>
+      </c>
+      <c r="D69" s="12">
+        <v>240</v>
+      </c>
+      <c r="E69" s="12">
+        <v>20</v>
+      </c>
+      <c r="F69" s="12">
+        <v>0</v>
+      </c>
+      <c r="G69" s="12">
+        <v>0</v>
+      </c>
+      <c r="H69" s="12">
+        <v>40</v>
+      </c>
+      <c r="I69" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="13" t="str">
+        <v>630</v>
+      </c>
+      <c r="J69" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="14"/>
-      <c r="L69" s="14"/>
-      <c r="M69" s="14"/>
-      <c r="N69" s="15"/>
+        <v>810</v>
+      </c>
+      <c r="K69" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L69" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M69" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N69" s="15" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>Feeling great today.</t>
+  </si>
+  <si>
+    <t>CA did not go well.</t>
   </si>
 </sst>
 </file>
@@ -4678,26 +4681,50 @@
       </c>
     </row>
     <row r="70" spans="1:14">
-      <c r="A70" s="11"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12"/>
-      <c r="I70" s="13" t="str">
+      <c r="A70" s="11">
+        <v>46307</v>
+      </c>
+      <c r="B70" s="12">
+        <v>390</v>
+      </c>
+      <c r="C70" s="12">
+        <v>30</v>
+      </c>
+      <c r="D70" s="12">
+        <v>440</v>
+      </c>
+      <c r="E70" s="12">
+        <v>20</v>
+      </c>
+      <c r="F70" s="12">
+        <v>0</v>
+      </c>
+      <c r="G70" s="12">
+        <v>0</v>
+      </c>
+      <c r="H70" s="12">
+        <v>20</v>
+      </c>
+      <c r="I70" s="13">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="13" t="str">
+        <v>900</v>
+      </c>
+      <c r="J70" s="13">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
-      <c r="M70" s="14"/>
-      <c r="N70" s="15"/>
+        <v>540</v>
+      </c>
+      <c r="K70" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L70" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="M70" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N70" s="15" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>CA did not go well.</t>
+  </si>
+  <si>
+    <t>My exam did not go very well.</t>
   </si>
 </sst>
 </file>
@@ -4727,26 +4730,50 @@
       </c>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" s="11"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12"/>
-      <c r="I71" s="13" t="str">
+      <c r="A71" s="11">
+        <v>46308</v>
+      </c>
+      <c r="B71" s="12">
+        <v>300</v>
+      </c>
+      <c r="C71" s="12">
+        <v>30</v>
+      </c>
+      <c r="D71" s="12">
+        <v>360</v>
+      </c>
+      <c r="E71" s="12">
+        <v>20</v>
+      </c>
+      <c r="F71" s="12">
+        <v>0</v>
+      </c>
+      <c r="G71" s="12">
+        <v>0</v>
+      </c>
+      <c r="H71" s="12">
+        <v>20</v>
+      </c>
+      <c r="I71" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="13" t="str">
+        <v>730</v>
+      </c>
+      <c r="J71" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="14"/>
-      <c r="L71" s="14"/>
-      <c r="M71" s="14"/>
-      <c r="N71" s="15"/>
+        <v>710</v>
+      </c>
+      <c r="K71" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L71" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M71" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N71" s="15" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>My exam did not go very well.</t>
+  </si>
+  <si>
+    <t>Today exam was good.</t>
   </si>
 </sst>
 </file>
@@ -4776,26 +4779,50 @@
       </c>
     </row>
     <row r="72" spans="1:14">
-      <c r="A72" s="11"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="12"/>
-      <c r="F72" s="12"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="12"/>
-      <c r="I72" s="13" t="str">
+      <c r="A72" s="11">
+        <v>46309</v>
+      </c>
+      <c r="B72" s="12">
+        <v>360</v>
+      </c>
+      <c r="C72" s="12">
+        <v>20</v>
+      </c>
+      <c r="D72" s="12">
+        <v>300</v>
+      </c>
+      <c r="E72" s="12">
+        <v>20</v>
+      </c>
+      <c r="F72" s="12">
+        <v>0</v>
+      </c>
+      <c r="G72" s="12">
+        <v>0</v>
+      </c>
+      <c r="H72" s="12">
+        <v>20</v>
+      </c>
+      <c r="I72" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="13" t="str">
+        <v>720</v>
+      </c>
+      <c r="J72" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="14"/>
-      <c r="L72" s="14"/>
-      <c r="M72" s="14"/>
-      <c r="N72" s="15"/>
+        <v>720</v>
+      </c>
+      <c r="K72" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L72" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M72" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N72" s="15" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>Today exam was good.</t>
+  </si>
+  <si>
+    <t>Preparing for exam.</t>
   </si>
 </sst>
 </file>
@@ -4825,26 +4828,50 @@
       </c>
     </row>
     <row r="73" spans="1:14">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12"/>
-      <c r="E73" s="12"/>
-      <c r="F73" s="12"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="12"/>
-      <c r="I73" s="13" t="str">
+      <c r="A73" s="11">
+        <v>46310</v>
+      </c>
+      <c r="B73" s="12">
+        <v>400</v>
+      </c>
+      <c r="C73" s="12">
+        <v>20</v>
+      </c>
+      <c r="D73" s="12">
+        <v>420</v>
+      </c>
+      <c r="E73" s="12">
+        <v>20</v>
+      </c>
+      <c r="F73" s="12">
+        <v>0</v>
+      </c>
+      <c r="G73" s="12">
+        <v>0</v>
+      </c>
+      <c r="H73" s="12">
+        <v>20</v>
+      </c>
+      <c r="I73" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="13" t="str">
+        <v>880</v>
+      </c>
+      <c r="J73" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="14"/>
-      <c r="L73" s="14"/>
-      <c r="M73" s="14"/>
-      <c r="N73" s="15"/>
+        <v>560</v>
+      </c>
+      <c r="K73" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L73" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M73" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N73" s="15" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t>Preparing for exam.</t>
+  </si>
+  <si>
+    <t>Feeling tired.</t>
   </si>
 </sst>
 </file>
@@ -4874,26 +4877,50 @@
       </c>
     </row>
     <row r="74" spans="1:14">
-      <c r="A74" s="11"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="12"/>
-      <c r="E74" s="12"/>
-      <c r="F74" s="12"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="12"/>
-      <c r="I74" s="13" t="str">
+      <c r="A74" s="11">
+        <v>46311</v>
+      </c>
+      <c r="B74" s="12">
+        <v>260</v>
+      </c>
+      <c r="C74" s="12">
+        <v>20</v>
+      </c>
+      <c r="D74" s="12">
+        <v>360</v>
+      </c>
+      <c r="E74" s="12">
+        <v>20</v>
+      </c>
+      <c r="F74" s="12">
+        <v>0</v>
+      </c>
+      <c r="G74" s="12">
+        <v>0</v>
+      </c>
+      <c r="H74" s="12">
+        <v>20</v>
+      </c>
+      <c r="I74" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="13" t="str">
+        <v>680</v>
+      </c>
+      <c r="J74" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="14"/>
-      <c r="L74" s="14"/>
-      <c r="M74" s="14"/>
-      <c r="N74" s="15"/>
+        <v>760</v>
+      </c>
+      <c r="K74" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L74" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M74" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N74" s="15" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -340,6 +340,9 @@
   </si>
   <si>
     <t>Feeling tired.</t>
+  </si>
+  <si>
+    <t>Enjoy today.</t>
   </si>
 </sst>
 </file>
@@ -4923,26 +4926,50 @@
       </c>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" s="11"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="12"/>
-      <c r="E75" s="12"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="12"/>
-      <c r="I75" s="13" t="str">
+      <c r="A75" s="11">
+        <v>46312</v>
+      </c>
+      <c r="B75" s="12">
+        <v>300</v>
+      </c>
+      <c r="C75" s="12">
+        <v>20</v>
+      </c>
+      <c r="D75" s="12">
+        <v>300</v>
+      </c>
+      <c r="E75" s="12">
+        <v>20</v>
+      </c>
+      <c r="F75" s="12">
+        <v>0</v>
+      </c>
+      <c r="G75" s="12">
+        <v>0</v>
+      </c>
+      <c r="H75" s="12">
+        <v>40</v>
+      </c>
+      <c r="I75" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="13" t="str">
+        <v>680</v>
+      </c>
+      <c r="J75" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="14"/>
-      <c r="L75" s="14"/>
-      <c r="M75" s="14"/>
-      <c r="N75" s="15"/>
+        <v>760</v>
+      </c>
+      <c r="K75" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L75" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M75" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N75" s="15" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4972,26 +4972,50 @@
       </c>
     </row>
     <row r="76" spans="1:14">
-      <c r="A76" s="11"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="12"/>
-      <c r="I76" s="13" t="str">
+      <c r="A76" s="11">
+        <v>46313</v>
+      </c>
+      <c r="B76" s="12">
+        <v>480</v>
+      </c>
+      <c r="C76" s="12">
+        <v>20</v>
+      </c>
+      <c r="D76" s="12">
+        <v>60</v>
+      </c>
+      <c r="E76" s="12">
+        <v>20</v>
+      </c>
+      <c r="F76" s="12">
+        <v>0</v>
+      </c>
+      <c r="G76" s="12">
+        <v>0</v>
+      </c>
+      <c r="H76" s="12">
+        <v>20</v>
+      </c>
+      <c r="I76" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="13" t="str">
+        <v>600</v>
+      </c>
+      <c r="J76" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="14"/>
-      <c r="L76" s="14"/>
-      <c r="M76" s="14"/>
-      <c r="N76" s="15"/>
+        <v>840</v>
+      </c>
+      <c r="K76" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L76" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M76" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N76" s="15" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5018,26 +5018,50 @@
       </c>
     </row>
     <row r="77" spans="1:14">
-      <c r="A77" s="11"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="12"/>
-      <c r="D77" s="12"/>
-      <c r="E77" s="12"/>
-      <c r="F77" s="12"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="12"/>
-      <c r="I77" s="13" t="str">
+      <c r="A77" s="11">
+        <v>46314</v>
+      </c>
+      <c r="B77" s="12">
+        <v>320</v>
+      </c>
+      <c r="C77" s="12">
+        <v>20</v>
+      </c>
+      <c r="D77" s="12">
+        <v>60</v>
+      </c>
+      <c r="E77" s="12">
+        <v>20</v>
+      </c>
+      <c r="F77" s="12">
+        <v>50</v>
+      </c>
+      <c r="G77" s="12">
+        <v>1</v>
+      </c>
+      <c r="H77" s="12">
+        <v>20</v>
+      </c>
+      <c r="I77" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="13" t="str">
+        <v>490</v>
+      </c>
+      <c r="J77" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="14"/>
-      <c r="L77" s="14"/>
-      <c r="M77" s="14"/>
-      <c r="N77" s="15"/>
+        <v>950</v>
+      </c>
+      <c r="K77" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L77" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M77" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N77" s="15" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5064,26 +5064,50 @@
       </c>
     </row>
     <row r="78" spans="1:14">
-      <c r="A78" s="11"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="12"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="12"/>
-      <c r="I78" s="13" t="str">
+      <c r="A78" s="11">
+        <v>46315</v>
+      </c>
+      <c r="B78" s="12">
+        <v>420</v>
+      </c>
+      <c r="C78" s="12">
+        <v>20</v>
+      </c>
+      <c r="D78" s="12">
+        <v>120</v>
+      </c>
+      <c r="E78" s="12">
+        <v>30</v>
+      </c>
+      <c r="F78" s="12">
+        <v>0</v>
+      </c>
+      <c r="G78" s="12">
+        <v>0</v>
+      </c>
+      <c r="H78" s="12">
+        <v>20</v>
+      </c>
+      <c r="I78" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="13" t="str">
+        <v>610</v>
+      </c>
+      <c r="J78" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="14"/>
-      <c r="L78" s="14"/>
-      <c r="M78" s="14"/>
-      <c r="N78" s="15"/>
+        <v>830</v>
+      </c>
+      <c r="K78" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L78" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M78" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N78" s="15" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5110,26 +5110,50 @@
       </c>
     </row>
     <row r="79" spans="1:14">
-      <c r="A79" s="11"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="12"/>
-      <c r="E79" s="12"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="12"/>
-      <c r="I79" s="13" t="str">
+      <c r="A79" s="11">
+        <v>46316</v>
+      </c>
+      <c r="B79" s="12">
+        <v>380</v>
+      </c>
+      <c r="C79" s="12">
+        <v>20</v>
+      </c>
+      <c r="D79" s="12">
+        <v>80</v>
+      </c>
+      <c r="E79" s="12">
+        <v>30</v>
+      </c>
+      <c r="F79" s="12">
+        <v>300</v>
+      </c>
+      <c r="G79" s="12">
+        <v>6</v>
+      </c>
+      <c r="H79" s="12">
+        <v>20</v>
+      </c>
+      <c r="I79" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="13" t="str">
+        <v>830</v>
+      </c>
+      <c r="J79" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="14"/>
-      <c r="L79" s="14"/>
-      <c r="M79" s="14"/>
-      <c r="N79" s="15"/>
+        <v>610</v>
+      </c>
+      <c r="K79" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L79" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M79" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="N79" s="15" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5156,26 +5156,50 @@
       </c>
     </row>
     <row r="80" spans="1:14">
-      <c r="A80" s="11"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="12"/>
-      <c r="E80" s="12"/>
-      <c r="F80" s="12"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="12"/>
-      <c r="I80" s="13" t="str">
+      <c r="A80" s="11">
+        <v>46317</v>
+      </c>
+      <c r="B80" s="12">
+        <v>360</v>
+      </c>
+      <c r="C80" s="12">
+        <v>20</v>
+      </c>
+      <c r="D80" s="12">
+        <v>120</v>
+      </c>
+      <c r="E80" s="12">
+        <v>30</v>
+      </c>
+      <c r="F80" s="12">
+        <v>150</v>
+      </c>
+      <c r="G80" s="12">
+        <v>3</v>
+      </c>
+      <c r="H80" s="12">
+        <v>20</v>
+      </c>
+      <c r="I80" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="13" t="str">
+        <v>700</v>
+      </c>
+      <c r="J80" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="14"/>
-      <c r="L80" s="14"/>
-      <c r="M80" s="14"/>
-      <c r="N80" s="15"/>
+        <v>740</v>
+      </c>
+      <c r="K80" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L80" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M80" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N80" s="15" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>Enjoy today.</t>
+  </si>
+  <si>
+    <t>I'm a little worried because of my C++ project.</t>
   </si>
 </sst>
 </file>
@@ -5201,27 +5204,51 @@
         <v>91</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
-      <c r="A81" s="11"/>
-      <c r="B81" s="12"/>
-      <c r="C81" s="12"/>
-      <c r="D81" s="12"/>
-      <c r="E81" s="12"/>
-      <c r="F81" s="12"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="12"/>
-      <c r="I81" s="13" t="str">
+    <row r="81" ht="30" spans="1:14">
+      <c r="A81" s="11">
+        <v>46318</v>
+      </c>
+      <c r="B81" s="12">
+        <v>360</v>
+      </c>
+      <c r="C81" s="12">
+        <v>20</v>
+      </c>
+      <c r="D81" s="12">
+        <v>150</v>
+      </c>
+      <c r="E81" s="12">
+        <v>30</v>
+      </c>
+      <c r="F81" s="12">
+        <v>150</v>
+      </c>
+      <c r="G81" s="12">
+        <v>3</v>
+      </c>
+      <c r="H81" s="12">
+        <v>20</v>
+      </c>
+      <c r="I81" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="13" t="str">
+        <v>730</v>
+      </c>
+      <c r="J81" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="14"/>
-      <c r="L81" s="14"/>
-      <c r="M81" s="14"/>
-      <c r="N81" s="15"/>
+        <v>710</v>
+      </c>
+      <c r="K81" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L81" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M81" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N81" s="15" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5251,26 +5251,50 @@
       </c>
     </row>
     <row r="82" spans="1:14">
-      <c r="A82" s="11"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
-      <c r="H82" s="12"/>
-      <c r="I82" s="13" t="str">
+      <c r="A82" s="11">
+        <v>46319</v>
+      </c>
+      <c r="B82" s="12">
+        <v>420</v>
+      </c>
+      <c r="C82" s="12">
+        <v>20</v>
+      </c>
+      <c r="D82" s="12">
+        <v>180</v>
+      </c>
+      <c r="E82" s="12">
+        <v>30</v>
+      </c>
+      <c r="F82" s="12">
+        <v>100</v>
+      </c>
+      <c r="G82" s="12">
+        <v>2</v>
+      </c>
+      <c r="H82" s="12">
+        <v>20</v>
+      </c>
+      <c r="I82" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="13" t="str">
+        <v>770</v>
+      </c>
+      <c r="J82" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K82" s="14"/>
-      <c r="L82" s="14"/>
-      <c r="M82" s="14"/>
-      <c r="N82" s="15"/>
+        <v>670</v>
+      </c>
+      <c r="K82" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L82" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M82" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N82" s="15" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t>I'm a little worried because of my C++ project.</t>
+  </si>
+  <si>
+    <t>Doing code.</t>
   </si>
 </sst>
 </file>
@@ -5297,26 +5300,50 @@
       </c>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="11"/>
-      <c r="B83" s="12"/>
-      <c r="C83" s="12"/>
-      <c r="D83" s="12"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="12"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="12"/>
-      <c r="I83" s="13" t="str">
+      <c r="A83" s="11">
+        <v>46320</v>
+      </c>
+      <c r="B83" s="12">
+        <v>360</v>
+      </c>
+      <c r="C83" s="12">
+        <v>20</v>
+      </c>
+      <c r="D83" s="12">
+        <v>150</v>
+      </c>
+      <c r="E83" s="12">
+        <v>180</v>
+      </c>
+      <c r="F83" s="12">
+        <v>0</v>
+      </c>
+      <c r="G83" s="12">
+        <v>0</v>
+      </c>
+      <c r="H83" s="12">
+        <v>20</v>
+      </c>
+      <c r="I83" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="13" t="str">
+        <v>730</v>
+      </c>
+      <c r="J83" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K83" s="14"/>
-      <c r="L83" s="14"/>
-      <c r="M83" s="14"/>
-      <c r="N83" s="15"/>
+        <v>710</v>
+      </c>
+      <c r="K83" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L83" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M83" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N83" s="15" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -349,6 +349,9 @@
   </si>
   <si>
     <t>Doing code.</t>
+  </si>
+  <si>
+    <t>Stress of project.</t>
   </si>
 </sst>
 </file>
@@ -5346,26 +5349,50 @@
       </c>
     </row>
     <row r="84" spans="1:14">
-      <c r="A84" s="11"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="12"/>
-      <c r="D84" s="12"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12"/>
-      <c r="H84" s="12"/>
-      <c r="I84" s="13" t="str">
+      <c r="A84" s="11">
+        <v>46321</v>
+      </c>
+      <c r="B84" s="12">
+        <v>450</v>
+      </c>
+      <c r="C84" s="12">
+        <v>20</v>
+      </c>
+      <c r="D84" s="12">
+        <v>400</v>
+      </c>
+      <c r="E84" s="12">
+        <v>120</v>
+      </c>
+      <c r="F84" s="12">
+        <v>0</v>
+      </c>
+      <c r="G84" s="12">
+        <v>0</v>
+      </c>
+      <c r="H84" s="12">
+        <v>20</v>
+      </c>
+      <c r="I84" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="13" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J84" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K84" s="14"/>
-      <c r="L84" s="14"/>
-      <c r="M84" s="14"/>
-      <c r="N84" s="15"/>
+        <v>430</v>
+      </c>
+      <c r="K84" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="L84" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M84" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N84" s="15" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5395,26 +5395,50 @@
       </c>
     </row>
     <row r="85" spans="1:14">
-      <c r="A85" s="11"/>
-      <c r="B85" s="12"/>
-      <c r="C85" s="12"/>
-      <c r="D85" s="12"/>
-      <c r="E85" s="12"/>
-      <c r="F85" s="12"/>
-      <c r="G85" s="12"/>
-      <c r="H85" s="12"/>
-      <c r="I85" s="13" t="str">
+      <c r="A85" s="11">
+        <v>46322</v>
+      </c>
+      <c r="B85" s="12">
+        <v>300</v>
+      </c>
+      <c r="C85" s="12">
+        <v>20</v>
+      </c>
+      <c r="D85" s="12">
+        <v>160</v>
+      </c>
+      <c r="E85" s="12">
+        <v>80</v>
+      </c>
+      <c r="F85" s="12">
+        <v>300</v>
+      </c>
+      <c r="G85" s="12">
+        <v>6</v>
+      </c>
+      <c r="H85" s="12">
+        <v>20</v>
+      </c>
+      <c r="I85" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J85" s="13" t="str">
+        <v>880</v>
+      </c>
+      <c r="J85" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K85" s="14"/>
-      <c r="L85" s="14"/>
-      <c r="M85" s="14"/>
-      <c r="N85" s="15"/>
+        <v>560</v>
+      </c>
+      <c r="K85" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L85" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M85" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N85" s="15" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5441,26 +5441,50 @@
       </c>
     </row>
     <row r="86" spans="1:14">
-      <c r="A86" s="11"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="12"/>
-      <c r="D86" s="12"/>
-      <c r="E86" s="12"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="12"/>
-      <c r="I86" s="13" t="str">
+      <c r="A86" s="11">
+        <v>46323</v>
+      </c>
+      <c r="B86" s="12">
+        <v>420</v>
+      </c>
+      <c r="C86" s="12">
+        <v>20</v>
+      </c>
+      <c r="D86" s="12">
+        <v>120</v>
+      </c>
+      <c r="E86" s="12">
+        <v>60</v>
+      </c>
+      <c r="F86" s="12">
+        <v>300</v>
+      </c>
+      <c r="G86" s="12">
+        <v>6</v>
+      </c>
+      <c r="H86" s="12">
+        <v>20</v>
+      </c>
+      <c r="I86" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J86" s="13" t="str">
+        <v>940</v>
+      </c>
+      <c r="J86" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K86" s="14"/>
-      <c r="L86" s="14"/>
-      <c r="M86" s="14"/>
-      <c r="N86" s="15"/>
+        <v>500</v>
+      </c>
+      <c r="K86" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L86" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M86" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N86" s="15" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5487,26 +5487,50 @@
       </c>
     </row>
     <row r="87" spans="1:14">
-      <c r="A87" s="11"/>
-      <c r="B87" s="12"/>
-      <c r="C87" s="12"/>
-      <c r="D87" s="12"/>
-      <c r="E87" s="12"/>
-      <c r="F87" s="12"/>
-      <c r="G87" s="12"/>
-      <c r="H87" s="12"/>
-      <c r="I87" s="13" t="str">
+      <c r="A87" s="11">
+        <v>46324</v>
+      </c>
+      <c r="B87" s="12">
+        <v>400</v>
+      </c>
+      <c r="C87" s="12">
+        <v>20</v>
+      </c>
+      <c r="D87" s="12">
+        <v>180</v>
+      </c>
+      <c r="E87" s="12">
+        <v>80</v>
+      </c>
+      <c r="F87" s="12">
+        <v>150</v>
+      </c>
+      <c r="G87" s="12">
+        <v>3</v>
+      </c>
+      <c r="H87" s="12">
+        <v>20</v>
+      </c>
+      <c r="I87" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J87" s="13" t="str">
+        <v>850</v>
+      </c>
+      <c r="J87" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K87" s="14"/>
-      <c r="L87" s="14"/>
-      <c r="M87" s="14"/>
-      <c r="N87" s="15"/>
+        <v>590</v>
+      </c>
+      <c r="K87" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L87" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M87" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N87" s="15" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="11"/>

--- a/12622124.xlsx
+++ b/12622124.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -5533,26 +5533,50 @@
       </c>
     </row>
     <row r="88" spans="1:14">
-      <c r="A88" s="11"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="12"/>
-      <c r="D88" s="12"/>
-      <c r="E88" s="12"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="12"/>
-      <c r="H88" s="12"/>
-      <c r="I88" s="13" t="str">
+      <c r="A88" s="11">
+        <v>46325</v>
+      </c>
+      <c r="B88" s="12">
+        <v>340</v>
+      </c>
+      <c r="C88" s="12">
+        <v>20</v>
+      </c>
+      <c r="D88" s="12">
+        <v>200</v>
+      </c>
+      <c r="E88" s="12">
+        <v>60</v>
+      </c>
+      <c r="F88" s="12">
+        <v>250</v>
+      </c>
+      <c r="G88" s="12">
+        <v>5</v>
+      </c>
+      <c r="H88" s="12">
+        <v>20</v>
+      </c>
+      <c r="I88" s="13">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J88" s="13" t="str">
+        <v>890</v>
+      </c>
+      <c r="J88" s="13">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K88" s="14"/>
-      <c r="L88" s="14"/>
-      <c r="M88" s="14"/>
-      <c r="N88" s="15"/>
+        <v>550</v>
+      </c>
+      <c r="K88" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L88" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="M88" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N88" s="15" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="11"/>
